--- a/Electronics/PCBs/Main/PickAndPlace.xlsx
+++ b/Electronics/PCBs/Main/PickAndPlace.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB-V1_2026-04-29" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB-V1_2026-05-11" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="291">
   <si>
     <t>Designator</t>
   </si>
@@ -241,165 +241,168 @@
     <t>CL10A105KO8NNNC</t>
   </si>
   <si>
-    <t>13.4mm</t>
+    <t>13.3mm</t>
+  </si>
+  <si>
+    <t>-26.3mm</t>
+  </si>
+  <si>
+    <t>12.6mm</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>CN-BAT</t>
+  </si>
+  <si>
+    <t>B4B-PH-K-S(LF)(SN)_C131334</t>
+  </si>
+  <si>
+    <t>CONN-TH_B4B-PH-K-S</t>
+  </si>
+  <si>
+    <t>54.3mm</t>
+  </si>
+  <si>
+    <t>-31.1mm</t>
+  </si>
+  <si>
+    <t>57.3mm</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>B4B-PH-K-S(LF)(SN)</t>
+  </si>
+  <si>
+    <t>CN-EARS</t>
+  </si>
+  <si>
+    <t>B2B-PH-K-S(LF)(SN)</t>
+  </si>
+  <si>
+    <t>CONN-TH_B2B-PH-K-S</t>
+  </si>
+  <si>
+    <t>21mm</t>
+  </si>
+  <si>
+    <t>-4mm</t>
+  </si>
+  <si>
+    <t>20mm</t>
+  </si>
+  <si>
+    <t>CN-IMU</t>
+  </si>
+  <si>
+    <t>-12.8mm</t>
+  </si>
+  <si>
+    <t>CN-LASER</t>
+  </si>
+  <si>
+    <t>-23.9mm</t>
+  </si>
+  <si>
+    <t>CN-MOTORS</t>
+  </si>
+  <si>
+    <t>B5B-PH-K-S(LF)(SN)</t>
+  </si>
+  <si>
+    <t>CONN-TH_B5B-PH-K-S-LF-SN</t>
+  </si>
+  <si>
+    <t>53.3mm</t>
+  </si>
+  <si>
+    <t>-19mm</t>
+  </si>
+  <si>
+    <t>CN-POWER</t>
+  </si>
+  <si>
+    <t>-10mm</t>
+  </si>
+  <si>
+    <t>CN-READER</t>
+  </si>
+  <si>
+    <t>B7B-PH-K-S(LF)(SN)</t>
+  </si>
+  <si>
+    <t>CONN-TH_B7B-PH-K-S-LF-SN</t>
+  </si>
+  <si>
+    <t>9mm</t>
+  </si>
+  <si>
+    <t>-34.5mm</t>
+  </si>
+  <si>
+    <t>3mm</t>
+  </si>
+  <si>
+    <t>CN-SCREEN</t>
+  </si>
+  <si>
+    <t>-37.5mm</t>
+  </si>
+  <si>
+    <t>CPGND</t>
+  </si>
+  <si>
+    <t>GR477M025F14RR0VL4FP0</t>
+  </si>
+  <si>
+    <t>CAP-TH_BD8.0-P3.50-D0.6-FD</t>
+  </si>
+  <si>
+    <t>16mm</t>
+  </si>
+  <si>
+    <t>17.75mm</t>
+  </si>
+  <si>
+    <t>470uF</t>
+  </si>
+  <si>
+    <t>CSPKRG</t>
+  </si>
+  <si>
+    <t>CL10B221KB8NNNC</t>
+  </si>
+  <si>
+    <t>6.3mm</t>
+  </si>
+  <si>
+    <t>-11.2mm</t>
+  </si>
+  <si>
+    <t>5.6mm</t>
+  </si>
+  <si>
+    <t>220pF</t>
+  </si>
+  <si>
+    <t>CSPKRV</t>
+  </si>
+  <si>
+    <t>9.7mm</t>
+  </si>
+  <si>
+    <t>CVREF</t>
+  </si>
+  <si>
+    <t>2.6mm</t>
   </si>
   <si>
     <t>-27.7mm</t>
   </si>
   <si>
-    <t>12.7mm</t>
-  </si>
-  <si>
-    <t>1uF</t>
-  </si>
-  <si>
-    <t>CN-BAT</t>
-  </si>
-  <si>
-    <t>B4B-PH-K-S(LF)(SN)_C131334</t>
-  </si>
-  <si>
-    <t>CONN-TH_B4B-PH-K-S</t>
-  </si>
-  <si>
-    <t>54.3mm</t>
-  </si>
-  <si>
-    <t>-31.1mm</t>
-  </si>
-  <si>
-    <t>57.3mm</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>B4B-PH-K-S(LF)(SN)</t>
-  </si>
-  <si>
-    <t>CN-EARS</t>
-  </si>
-  <si>
-    <t>B2B-PH-K-S(LF)(SN)</t>
-  </si>
-  <si>
-    <t>CONN-TH_B2B-PH-K-S</t>
-  </si>
-  <si>
-    <t>21mm</t>
-  </si>
-  <si>
-    <t>-10mm</t>
-  </si>
-  <si>
-    <t>20mm</t>
-  </si>
-  <si>
-    <t>CN-IMU</t>
-  </si>
-  <si>
-    <t>-12.8mm</t>
-  </si>
-  <si>
-    <t>CN-LASER</t>
-  </si>
-  <si>
-    <t>-23.9mm</t>
-  </si>
-  <si>
-    <t>CN-MOTORS</t>
-  </si>
-  <si>
-    <t>B5B-PH-K-S(LF)(SN)</t>
-  </si>
-  <si>
-    <t>CONN-TH_B5B-PH-K-S-LF-SN</t>
-  </si>
-  <si>
-    <t>53.3mm</t>
-  </si>
-  <si>
-    <t>-19mm</t>
-  </si>
-  <si>
-    <t>CN-POWER</t>
-  </si>
-  <si>
-    <t>-4mm</t>
-  </si>
-  <si>
-    <t>CN-READER</t>
-  </si>
-  <si>
-    <t>B7B-PH-K-S(LF)(SN)</t>
-  </si>
-  <si>
-    <t>CONN-TH_B7B-PH-K-S-LF-SN</t>
-  </si>
-  <si>
-    <t>9mm</t>
-  </si>
-  <si>
-    <t>-34.5mm</t>
-  </si>
-  <si>
-    <t>3mm</t>
-  </si>
-  <si>
-    <t>CN-SCREEN</t>
-  </si>
-  <si>
-    <t>-37.5mm</t>
-  </si>
-  <si>
-    <t>CPGND</t>
-  </si>
-  <si>
-    <t>GR477M025F14RR0VL4FP0</t>
-  </si>
-  <si>
-    <t>CAP-TH_BD8.0-P3.50-D0.6-FD</t>
-  </si>
-  <si>
-    <t>16.5mm</t>
-  </si>
-  <si>
-    <t>18.25mm</t>
-  </si>
-  <si>
-    <t>470uF</t>
-  </si>
-  <si>
-    <t>CSPKRG</t>
-  </si>
-  <si>
-    <t>CL10B221KB8NNNC</t>
-  </si>
-  <si>
-    <t>6.3mm</t>
-  </si>
-  <si>
-    <t>-11.2mm</t>
-  </si>
-  <si>
-    <t>5.6mm</t>
-  </si>
-  <si>
-    <t>220pF</t>
-  </si>
-  <si>
-    <t>CSPKRV</t>
-  </si>
-  <si>
-    <t>9.7mm</t>
-  </si>
-  <si>
-    <t>CVREF</t>
-  </si>
-  <si>
-    <t>2.6mm</t>
-  </si>
-  <si>
     <t>1.9mm</t>
   </si>
   <si>
@@ -832,13 +835,10 @@
     <t>RINR</t>
   </si>
   <si>
-    <t>15.8mm</t>
-  </si>
-  <si>
-    <t>-28.9mm</t>
-  </si>
-  <si>
-    <t>-29.653mm</t>
+    <t>-29.1mm</t>
+  </si>
+  <si>
+    <t>12.547mm</t>
   </si>
   <si>
     <t>CUPEN1</t>
@@ -859,9 +859,6 @@
     <t>0603B103K500NT</t>
   </si>
   <si>
-    <t>-29.5mm</t>
-  </si>
-  <si>
     <t>10nF</t>
   </si>
   <si>
@@ -871,13 +868,22 @@
     <t>0603WAF2202T5E</t>
   </si>
   <si>
-    <t>-26mm</t>
-  </si>
-  <si>
-    <t>12.647mm</t>
+    <t>-24.9mm</t>
   </si>
   <si>
     <t>22kΩ</t>
+  </si>
+  <si>
+    <t>CASIG</t>
+  </si>
+  <si>
+    <t>20.9mm</t>
+  </si>
+  <si>
+    <t>-18.2mm</t>
+  </si>
+  <si>
+    <t>21.6mm</t>
   </si>
 </sst>
 </file>
@@ -1254,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="14" width="20" customWidth="1"/>
@@ -2330,19 +2336,19 @@
         <v>128</v>
       </c>
       <c r="E25" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="F25" t="s">
         <v>128</v>
       </c>
       <c r="G25" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="H25" t="s">
+        <v>130</v>
+      </c>
+      <c r="I25" t="s">
         <v>129</v>
-      </c>
-      <c r="I25" t="s">
-        <v>77</v>
       </c>
       <c r="J25">
         <v>2</v>
@@ -2362,31 +2368,31 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B26" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E26" t="s">
         <v>27</v>
       </c>
       <c r="F26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G26" t="s">
         <v>27</v>
       </c>
       <c r="H26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -2401,36 +2407,36 @@
         <v>22</v>
       </c>
       <c r="N26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B27" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E27" t="s">
         <v>27</v>
       </c>
       <c r="F27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G27" t="s">
         <v>27</v>
       </c>
       <c r="H27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I27" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J27">
         <v>2</v>
@@ -2445,36 +2451,36 @@
         <v>22</v>
       </c>
       <c r="N27" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E28" t="s">
+        <v>143</v>
+      </c>
+      <c r="F28" t="s">
         <v>142</v>
       </c>
-      <c r="F28" t="s">
-        <v>141</v>
-      </c>
       <c r="G28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H28" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J28">
         <v>49</v>
@@ -2489,12 +2495,12 @@
         <v>22</v>
       </c>
       <c r="N28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B29" t="s">
         <v>99</v>
@@ -2503,19 +2509,19 @@
         <v>100</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E29" t="s">
         <v>43</v>
       </c>
       <c r="F29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G29" t="s">
         <v>43</v>
       </c>
       <c r="H29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I29" t="s">
         <v>39</v>
@@ -2538,31 +2544,31 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C30" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D30" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E30" t="s">
+        <v>152</v>
+      </c>
+      <c r="F30" t="s">
         <v>151</v>
       </c>
-      <c r="F30" t="s">
-        <v>150</v>
-      </c>
       <c r="G30" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H30" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J30">
         <v>16</v>
@@ -2577,36 +2583,36 @@
         <v>22</v>
       </c>
       <c r="N30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B31" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C31" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E31" t="s">
+        <v>159</v>
+      </c>
+      <c r="F31" t="s">
         <v>158</v>
       </c>
-      <c r="F31" t="s">
-        <v>157</v>
-      </c>
       <c r="G31" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H31" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I31" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J31">
         <v>3</v>
@@ -2621,36 +2627,36 @@
         <v>22</v>
       </c>
       <c r="N31" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B32" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C32" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D32" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E32" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F32" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G32" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H32" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I32" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J32">
         <v>3</v>
@@ -2665,36 +2671,36 @@
         <v>22</v>
       </c>
       <c r="N32" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B33" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E33" t="s">
+        <v>170</v>
+      </c>
+      <c r="F33" t="s">
         <v>169</v>
       </c>
-      <c r="F33" t="s">
-        <v>168</v>
-      </c>
       <c r="G33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H33" t="s">
+        <v>171</v>
+      </c>
+      <c r="I33" t="s">
         <v>170</v>
-      </c>
-      <c r="I33" t="s">
-        <v>169</v>
       </c>
       <c r="J33">
         <v>2</v>
@@ -2709,36 +2715,36 @@
         <v>22</v>
       </c>
       <c r="N33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B34" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C34" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D34" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E34" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F34" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G34" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H34" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I34" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J34">
         <v>2</v>
@@ -2753,36 +2759,36 @@
         <v>22</v>
       </c>
       <c r="N34" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C35" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D35" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F35" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H35" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J35">
         <v>2</v>
@@ -2797,36 +2803,36 @@
         <v>22</v>
       </c>
       <c r="N35" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B36" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C36" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D36" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E36" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F36" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G36" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H36" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I36" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J36">
         <v>2</v>
@@ -2841,36 +2847,36 @@
         <v>22</v>
       </c>
       <c r="N36" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B37" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C37" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D37" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F37" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H37" t="s">
+        <v>183</v>
+      </c>
+      <c r="I37" t="s">
         <v>182</v>
-      </c>
-      <c r="I37" t="s">
-        <v>181</v>
       </c>
       <c r="J37">
         <v>2</v>
@@ -2885,36 +2891,36 @@
         <v>40</v>
       </c>
       <c r="N37" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B38" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D38" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E38" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="F38" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G38" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="H38" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I38" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J38">
         <v>16</v>
@@ -2929,36 +2935,36 @@
         <v>40</v>
       </c>
       <c r="N38" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B39" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C39" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D39" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E39" t="s">
+        <v>194</v>
+      </c>
+      <c r="F39" t="s">
         <v>193</v>
       </c>
-      <c r="F39" t="s">
-        <v>192</v>
-      </c>
       <c r="G39" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H39" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I39" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J39">
         <v>6</v>
@@ -2973,36 +2979,36 @@
         <v>22</v>
       </c>
       <c r="N39" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C40" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E40" t="s">
+        <v>202</v>
+      </c>
+      <c r="F40" t="s">
         <v>201</v>
       </c>
-      <c r="F40" t="s">
-        <v>200</v>
-      </c>
       <c r="G40" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H40" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I40" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J40">
         <v>3</v>
@@ -3017,36 +3023,36 @@
         <v>22</v>
       </c>
       <c r="N40" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B41" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C41" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D41" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F41" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H41" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I41" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J41">
         <v>3</v>
@@ -3061,33 +3067,33 @@
         <v>22</v>
       </c>
       <c r="N41" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B42" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C42" t="s">
         <v>53</v>
       </c>
       <c r="D42" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E42" t="s">
         <v>55</v>
       </c>
       <c r="F42" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G42" t="s">
         <v>55</v>
       </c>
       <c r="H42" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I42" t="s">
         <v>56</v>
@@ -3105,33 +3111,33 @@
         <v>22</v>
       </c>
       <c r="N42" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B43" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C43" t="s">
         <v>53</v>
       </c>
       <c r="D43" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E43" t="s">
         <v>63</v>
       </c>
       <c r="F43" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G43" t="s">
         <v>63</v>
       </c>
       <c r="H43" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I43" t="s">
         <v>64</v>
@@ -3149,15 +3155,15 @@
         <v>22</v>
       </c>
       <c r="N43" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B44" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C44" t="s">
         <v>53</v>
@@ -3166,19 +3172,19 @@
         <v>66</v>
       </c>
       <c r="E44" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F44" t="s">
         <v>66</v>
       </c>
       <c r="G44" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H44" t="s">
         <v>68</v>
       </c>
       <c r="I44" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J44">
         <v>2</v>
@@ -3193,36 +3199,36 @@
         <v>22</v>
       </c>
       <c r="N44" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B45" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C45" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D45" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E45" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F45" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G45" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H45" t="s">
+        <v>222</v>
+      </c>
+      <c r="I45" t="s">
         <v>221</v>
-      </c>
-      <c r="I45" t="s">
-        <v>220</v>
       </c>
       <c r="J45">
         <v>2</v>
@@ -3237,36 +3243,36 @@
         <v>22</v>
       </c>
       <c r="N45" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B46" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C46" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D46" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E46" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F46" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G46" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H46" t="s">
+        <v>226</v>
+      </c>
+      <c r="I46" t="s">
         <v>225</v>
-      </c>
-      <c r="I46" t="s">
-        <v>224</v>
       </c>
       <c r="J46">
         <v>2</v>
@@ -3281,36 +3287,36 @@
         <v>22</v>
       </c>
       <c r="N46" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B47" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C47" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D47" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E47" t="s">
+        <v>229</v>
+      </c>
+      <c r="F47" t="s">
         <v>228</v>
       </c>
-      <c r="F47" t="s">
-        <v>227</v>
-      </c>
       <c r="G47" t="s">
+        <v>229</v>
+      </c>
+      <c r="H47" t="s">
         <v>228</v>
       </c>
-      <c r="H47" t="s">
-        <v>227</v>
-      </c>
       <c r="I47" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J47">
         <v>2</v>
@@ -3325,36 +3331,36 @@
         <v>22</v>
       </c>
       <c r="N47" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B48" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C48" t="s">
         <v>53</v>
       </c>
       <c r="D48" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E48" t="s">
+        <v>233</v>
+      </c>
+      <c r="F48" t="s">
         <v>232</v>
       </c>
-      <c r="F48" t="s">
-        <v>231</v>
-      </c>
       <c r="G48" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H48" t="s">
+        <v>234</v>
+      </c>
+      <c r="I48" t="s">
         <v>233</v>
-      </c>
-      <c r="I48" t="s">
-        <v>232</v>
       </c>
       <c r="J48">
         <v>2</v>
@@ -3369,36 +3375,36 @@
         <v>22</v>
       </c>
       <c r="N48" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B49" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C49" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D49" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E49" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F49" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G49" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H49" t="s">
+        <v>238</v>
+      </c>
+      <c r="I49" t="s">
         <v>237</v>
-      </c>
-      <c r="I49" t="s">
-        <v>236</v>
       </c>
       <c r="J49">
         <v>2</v>
@@ -3413,36 +3419,36 @@
         <v>22</v>
       </c>
       <c r="N49" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B50" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C50" t="s">
         <v>53</v>
       </c>
       <c r="D50" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E50" t="s">
+        <v>243</v>
+      </c>
+      <c r="F50" t="s">
         <v>242</v>
       </c>
-      <c r="F50" t="s">
-        <v>241</v>
-      </c>
       <c r="G50" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H50" t="s">
+        <v>244</v>
+      </c>
+      <c r="I50" t="s">
         <v>243</v>
-      </c>
-      <c r="I50" t="s">
-        <v>242</v>
       </c>
       <c r="J50">
         <v>2</v>
@@ -3457,36 +3463,36 @@
         <v>22</v>
       </c>
       <c r="N50" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B51" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C51" t="s">
         <v>53</v>
       </c>
       <c r="D51" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E51" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F51" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G51" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H51" t="s">
+        <v>248</v>
+      </c>
+      <c r="I51" t="s">
         <v>247</v>
-      </c>
-      <c r="I51" t="s">
-        <v>246</v>
       </c>
       <c r="J51">
         <v>2</v>
@@ -3501,15 +3507,15 @@
         <v>22</v>
       </c>
       <c r="N51" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B52" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C52" t="s">
         <v>53</v>
@@ -3518,19 +3524,19 @@
         <v>128</v>
       </c>
       <c r="E52" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F52" t="s">
         <v>128</v>
       </c>
       <c r="G52" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H52" t="s">
+        <v>251</v>
+      </c>
+      <c r="I52" t="s">
         <v>250</v>
-      </c>
-      <c r="I52" t="s">
-        <v>249</v>
       </c>
       <c r="J52">
         <v>2</v>
@@ -3545,36 +3551,36 @@
         <v>22</v>
       </c>
       <c r="N52" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B53" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C53" t="s">
         <v>53</v>
       </c>
       <c r="D53" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E53" t="s">
+        <v>254</v>
+      </c>
+      <c r="F53" t="s">
         <v>253</v>
       </c>
-      <c r="F53" t="s">
-        <v>252</v>
-      </c>
       <c r="G53" t="s">
+        <v>254</v>
+      </c>
+      <c r="H53" t="s">
         <v>253</v>
       </c>
-      <c r="H53" t="s">
-        <v>252</v>
-      </c>
       <c r="I53" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J53">
         <v>2</v>
@@ -3589,36 +3595,36 @@
         <v>22</v>
       </c>
       <c r="N53" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B54" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C54" t="s">
         <v>53</v>
       </c>
       <c r="D54" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E54" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F54" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G54" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H54" t="s">
+        <v>258</v>
+      </c>
+      <c r="I54" t="s">
         <v>257</v>
-      </c>
-      <c r="I54" t="s">
-        <v>256</v>
       </c>
       <c r="J54">
         <v>2</v>
@@ -3633,36 +3639,36 @@
         <v>22</v>
       </c>
       <c r="N54" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B55" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C55" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E55" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F55" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G55" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H55" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I55" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J55">
         <v>2</v>
@@ -3677,36 +3683,36 @@
         <v>22</v>
       </c>
       <c r="N55" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B56" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C56" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D56" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E56" t="s">
+        <v>266</v>
+      </c>
+      <c r="F56" t="s">
         <v>265</v>
       </c>
-      <c r="F56" t="s">
-        <v>264</v>
-      </c>
       <c r="G56" t="s">
+        <v>266</v>
+      </c>
+      <c r="H56" t="s">
         <v>265</v>
       </c>
-      <c r="H56" t="s">
-        <v>264</v>
-      </c>
       <c r="I56" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J56">
         <v>2</v>
@@ -3721,36 +3727,36 @@
         <v>22</v>
       </c>
       <c r="N56" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B57" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C57" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D57" t="s">
         <v>108</v>
       </c>
       <c r="E57" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F57" t="s">
         <v>108</v>
       </c>
       <c r="G57" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H57" t="s">
         <v>108</v>
       </c>
       <c r="I57" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J57">
         <v>2</v>
@@ -3765,36 +3771,36 @@
         <v>22</v>
       </c>
       <c r="N57" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B58" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C58" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D58" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E58" t="s">
         <v>39</v>
       </c>
       <c r="F58" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G58" t="s">
         <v>39</v>
       </c>
       <c r="H58" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I58" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J58">
         <v>2</v>
@@ -3809,36 +3815,36 @@
         <v>22</v>
       </c>
       <c r="N58" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B59" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C59" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D59" t="s">
-        <v>273</v>
+        <v>76</v>
       </c>
       <c r="E59" t="s">
         <v>274</v>
       </c>
       <c r="F59" t="s">
-        <v>273</v>
+        <v>76</v>
       </c>
       <c r="G59" t="s">
         <v>274</v>
       </c>
       <c r="H59" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I59" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J59">
         <v>2</v>
@@ -3847,13 +3853,13 @@
         <v>21</v>
       </c>
       <c r="L59">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M59" t="s">
         <v>22</v>
       </c>
       <c r="N59" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -3914,19 +3920,19 @@
         <v>76</v>
       </c>
       <c r="E61" t="s">
-        <v>282</v>
+        <v>129</v>
       </c>
       <c r="F61" t="s">
         <v>76</v>
       </c>
       <c r="G61" t="s">
-        <v>282</v>
+        <v>129</v>
       </c>
       <c r="H61" t="s">
         <v>78</v>
       </c>
       <c r="I61" t="s">
-        <v>282</v>
+        <v>129</v>
       </c>
       <c r="J61">
         <v>2</v>
@@ -3941,36 +3947,36 @@
         <v>22</v>
       </c>
       <c r="N61" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>283</v>
+      </c>
+      <c r="B62" t="s">
         <v>284</v>
       </c>
-      <c r="B62" t="s">
-        <v>285</v>
-      </c>
       <c r="C62" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D62" t="s">
         <v>76</v>
       </c>
       <c r="E62" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F62" t="s">
         <v>76</v>
       </c>
       <c r="G62" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H62" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="I62" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J62">
         <v>2</v>
@@ -3985,7 +3991,51 @@
         <v>22</v>
       </c>
       <c r="N62" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>287</v>
+      </c>
+      <c r="B63" t="s">
+        <v>120</v>
+      </c>
+      <c r="C63" t="s">
+        <v>53</v>
+      </c>
+      <c r="D63" t="s">
         <v>288</v>
+      </c>
+      <c r="E63" t="s">
+        <v>289</v>
+      </c>
+      <c r="F63" t="s">
+        <v>288</v>
+      </c>
+      <c r="G63" t="s">
+        <v>289</v>
+      </c>
+      <c r="H63" t="s">
+        <v>290</v>
+      </c>
+      <c r="I63" t="s">
+        <v>289</v>
+      </c>
+      <c r="J63">
+        <v>2</v>
+      </c>
+      <c r="K63" t="s">
+        <v>21</v>
+      </c>
+      <c r="L63">
+        <v>180</v>
+      </c>
+      <c r="M63" t="s">
+        <v>22</v>
+      </c>
+      <c r="N63" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/Electronics/PCBs/Main/PickAndPlace.xlsx
+++ b/Electronics/PCBs/Main/PickAndPlace.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB-V1_2026-05-11" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB_2026-05-27" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="301">
   <si>
     <t>Designator</t>
   </si>
@@ -277,7 +277,34 @@
     <t>B4B-PH-K-S(LF)(SN)</t>
   </si>
   <si>
-    <t>CN-EARS</t>
+    <t>CN-IMU</t>
+  </si>
+  <si>
+    <t>-12.8mm</t>
+  </si>
+  <si>
+    <t>CN-LASER</t>
+  </si>
+  <si>
+    <t>-23.9mm</t>
+  </si>
+  <si>
+    <t>CN-MOTORS</t>
+  </si>
+  <si>
+    <t>B5B-PH-K-S(LF)(SN)</t>
+  </si>
+  <si>
+    <t>CONN-TH_B5B-PH-K-S-LF-SN</t>
+  </si>
+  <si>
+    <t>53.3mm</t>
+  </si>
+  <si>
+    <t>-19mm</t>
+  </si>
+  <si>
+    <t>CN-POWER</t>
   </si>
   <si>
     <t>B2B-PH-K-S(LF)(SN)</t>
@@ -286,46 +313,13 @@
     <t>CONN-TH_B2B-PH-K-S</t>
   </si>
   <si>
-    <t>21mm</t>
+    <t>14.9mm</t>
   </si>
   <si>
     <t>-4mm</t>
   </si>
   <si>
-    <t>20mm</t>
-  </si>
-  <si>
-    <t>CN-IMU</t>
-  </si>
-  <si>
-    <t>-12.8mm</t>
-  </si>
-  <si>
-    <t>CN-LASER</t>
-  </si>
-  <si>
-    <t>-23.9mm</t>
-  </si>
-  <si>
-    <t>CN-MOTORS</t>
-  </si>
-  <si>
-    <t>B5B-PH-K-S(LF)(SN)</t>
-  </si>
-  <si>
-    <t>CONN-TH_B5B-PH-K-S-LF-SN</t>
-  </si>
-  <si>
-    <t>53.3mm</t>
-  </si>
-  <si>
-    <t>-19mm</t>
-  </si>
-  <si>
-    <t>CN-POWER</t>
-  </si>
-  <si>
-    <t>-10mm</t>
+    <t>13.9mm</t>
   </si>
   <si>
     <t>CN-READER</t>
@@ -361,10 +355,10 @@
     <t>CAP-TH_BD8.0-P3.50-D0.6-FD</t>
   </si>
   <si>
-    <t>16mm</t>
-  </si>
-  <si>
-    <t>17.75mm</t>
+    <t>15mm</t>
+  </si>
+  <si>
+    <t>16.75mm</t>
   </si>
   <si>
     <t>470uF</t>
@@ -415,10 +409,13 @@
     <t>SMA_L4.3-W2.6-LS5.2-RD</t>
   </si>
   <si>
-    <t>27.5mm</t>
-  </si>
-  <si>
-    <t>-17.2mm</t>
+    <t>22.5mm</t>
+  </si>
+  <si>
+    <t>-6mm</t>
+  </si>
+  <si>
+    <t>-8.2mm</t>
   </si>
   <si>
     <t>SS34</t>
@@ -427,7 +424,7 @@
     <t>D2</t>
   </si>
   <si>
-    <t>24mm</t>
+    <t>19mm</t>
   </si>
   <si>
     <t>ESP32-S3</t>
@@ -739,9 +736,6 @@
     <t>CL10C150JB8NNNC</t>
   </si>
   <si>
-    <t>22.5mm</t>
-  </si>
-  <si>
     <t>-45.7mm</t>
   </si>
   <si>
@@ -884,6 +878,42 @@
   </si>
   <si>
     <t>21.6mm</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>SMAJ5.0A_C10758</t>
+  </si>
+  <si>
+    <t>27mm</t>
+  </si>
+  <si>
+    <t>-12.5mm</t>
+  </si>
+  <si>
+    <t>-10.3mm</t>
+  </si>
+  <si>
+    <t>SMAJ5.0A</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>SMD1812P150TF/16_C20810</t>
+  </si>
+  <si>
+    <t>F1812</t>
+  </si>
+  <si>
+    <t>22mm</t>
+  </si>
+  <si>
+    <t>-10.647mm</t>
+  </si>
+  <si>
+    <t>SMD1812P150TF/16</t>
   </si>
 </sst>
 </file>
@@ -1260,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="14" width="20" customWidth="1"/>
@@ -1887,48 +1917,48 @@
         <v>88</v>
       </c>
       <c r="B15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" t="s">
         <v>89</v>
       </c>
-      <c r="C15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" t="s">
-        <v>91</v>
-      </c>
-      <c r="E15" t="s">
-        <v>92</v>
-      </c>
       <c r="F15" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="I15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K15" t="s">
         <v>86</v>
       </c>
       <c r="L15">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M15" t="s">
         <v>40</v>
       </c>
       <c r="N15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B16" t="s">
         <v>81</v>
@@ -1940,25 +1970,25 @@
         <v>83</v>
       </c>
       <c r="E16" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F16" t="s">
         <v>83</v>
       </c>
       <c r="G16" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H16" t="s">
         <v>85</v>
       </c>
       <c r="I16" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J16">
         <v>4</v>
       </c>
       <c r="K16" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1972,37 +2002,37 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" t="s">
         <v>96</v>
       </c>
-      <c r="B17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" t="s">
-        <v>83</v>
-      </c>
-      <c r="E17" t="s">
-        <v>97</v>
-      </c>
       <c r="F17" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H17" t="s">
         <v>85</v>
       </c>
       <c r="I17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K17" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2011,51 +2041,51 @@
         <v>40</v>
       </c>
       <c r="N17" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" t="s">
         <v>98</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>99</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>100</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>101</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
+        <v>100</v>
+      </c>
+      <c r="G18" t="s">
+        <v>101</v>
+      </c>
+      <c r="H18" t="s">
         <v>102</v>
       </c>
-      <c r="F18" t="s">
+      <c r="I18" t="s">
         <v>101</v>
       </c>
-      <c r="G18" t="s">
-        <v>102</v>
-      </c>
-      <c r="H18" t="s">
-        <v>85</v>
-      </c>
-      <c r="I18" t="s">
-        <v>102</v>
-      </c>
       <c r="J18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K18" t="s">
         <v>86</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M18" t="s">
         <v>40</v>
       </c>
       <c r="N18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -2063,31 +2093,31 @@
         <v>103</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="E19" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F19" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="G19" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H19" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="I19" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K19" t="s">
         <v>86</v>
@@ -2099,51 +2129,51 @@
         <v>40</v>
       </c>
       <c r="N19" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F20" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="G20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I20" t="s">
         <v>110</v>
       </c>
-      <c r="I20" t="s">
-        <v>109</v>
-      </c>
       <c r="J20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K20" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="L20">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M20" t="s">
         <v>40</v>
       </c>
       <c r="N20" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -2151,72 +2181,72 @@
         <v>111</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E21" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G21" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="H21" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="I21" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K21" t="s">
         <v>21</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M21" t="s">
         <v>40</v>
       </c>
       <c r="N21" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B22" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E22" t="s">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="F22" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G22" t="s">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="H22" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I22" t="s">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="J22">
         <v>2</v>
@@ -2225,42 +2255,42 @@
         <v>21</v>
       </c>
       <c r="L22">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="N22" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C23" t="s">
         <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F23" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H23" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="I23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J23">
         <v>2</v>
@@ -2275,7 +2305,7 @@
         <v>22</v>
       </c>
       <c r="N23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -2283,7 +2313,7 @@
         <v>125</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
         <v>53</v>
@@ -2292,19 +2322,19 @@
         <v>126</v>
       </c>
       <c r="E24" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F24" t="s">
         <v>126</v>
       </c>
       <c r="G24" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="H24" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="I24" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -2319,36 +2349,36 @@
         <v>22</v>
       </c>
       <c r="N24" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="D25" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E25" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F25" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G25" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="H25" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I25" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J25">
         <v>2</v>
@@ -2357,42 +2387,42 @@
         <v>21</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M25" t="s">
         <v>22</v>
       </c>
       <c r="N25" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" t="s">
         <v>131</v>
       </c>
-      <c r="B26" t="s">
-        <v>132</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
+        <v>137</v>
+      </c>
+      <c r="E26" t="s">
         <v>133</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
+        <v>137</v>
+      </c>
+      <c r="G26" t="s">
+        <v>133</v>
+      </c>
+      <c r="H26" t="s">
+        <v>137</v>
+      </c>
+      <c r="I26" t="s">
         <v>134</v>
-      </c>
-      <c r="E26" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" t="s">
-        <v>134</v>
-      </c>
-      <c r="G26" t="s">
-        <v>27</v>
-      </c>
-      <c r="H26" t="s">
-        <v>134</v>
-      </c>
-      <c r="I26" t="s">
-        <v>135</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -2407,39 +2437,39 @@
         <v>22</v>
       </c>
       <c r="N26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B27" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C27" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D27" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E27" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="F27" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G27" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="H27" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I27" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="K27" t="s">
         <v>21</v>
@@ -2451,83 +2481,83 @@
         <v>22</v>
       </c>
       <c r="N27" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B28" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E28" t="s">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="F28" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G28" t="s">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="H28" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I28" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="J28">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="K28" t="s">
         <v>21</v>
       </c>
       <c r="L28">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M28" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="N28" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>149</v>
       </c>
       <c r="D29" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E29" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
       <c r="F29" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G29" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
       <c r="H29" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I29" t="s">
-        <v>39</v>
+        <v>153</v>
       </c>
       <c r="J29">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="K29" t="s">
         <v>21</v>
@@ -2536,83 +2566,83 @@
         <v>270</v>
       </c>
       <c r="M29" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="N29" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B30" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C30" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D30" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E30" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F30" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G30" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="H30" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="I30" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="J30">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K30" t="s">
         <v>21</v>
       </c>
       <c r="L30">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M30" t="s">
         <v>22</v>
       </c>
       <c r="N30" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" t="s">
         <v>155</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>156</v>
       </c>
-      <c r="C31" t="s">
-        <v>157</v>
-      </c>
       <c r="D31" t="s">
+        <v>162</v>
+      </c>
+      <c r="E31" t="s">
         <v>158</v>
       </c>
-      <c r="E31" t="s">
-        <v>159</v>
-      </c>
       <c r="F31" t="s">
+        <v>162</v>
+      </c>
+      <c r="G31" t="s">
         <v>158</v>
       </c>
-      <c r="G31" t="s">
-        <v>159</v>
-      </c>
       <c r="H31" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I31" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J31">
         <v>3</v>
@@ -2621,45 +2651,45 @@
         <v>21</v>
       </c>
       <c r="L31">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M31" t="s">
         <v>22</v>
       </c>
       <c r="N31" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B32" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C32" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D32" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E32" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="F32" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G32" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H32" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I32" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="J32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K32" t="s">
         <v>21</v>
@@ -2671,36 +2701,36 @@
         <v>22</v>
       </c>
       <c r="N32" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>172</v>
+      </c>
+      <c r="B33" t="s">
         <v>166</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>167</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>168</v>
       </c>
-      <c r="D33" t="s">
-        <v>169</v>
-      </c>
       <c r="E33" t="s">
+        <v>173</v>
+      </c>
+      <c r="F33" t="s">
+        <v>168</v>
+      </c>
+      <c r="G33" t="s">
+        <v>173</v>
+      </c>
+      <c r="H33" t="s">
         <v>170</v>
       </c>
-      <c r="F33" t="s">
-        <v>169</v>
-      </c>
-      <c r="G33" t="s">
-        <v>170</v>
-      </c>
-      <c r="H33" t="s">
-        <v>171</v>
-      </c>
       <c r="I33" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J33">
         <v>2</v>
@@ -2715,36 +2745,36 @@
         <v>22</v>
       </c>
       <c r="N33" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B34" t="s">
+        <v>166</v>
+      </c>
+      <c r="C34" t="s">
         <v>167</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>168</v>
       </c>
-      <c r="D34" t="s">
-        <v>169</v>
-      </c>
       <c r="E34" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G34" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H34" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I34" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J34">
         <v>2</v>
@@ -2759,36 +2789,36 @@
         <v>22</v>
       </c>
       <c r="N34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B35" t="s">
+        <v>166</v>
+      </c>
+      <c r="C35" t="s">
         <v>167</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>168</v>
       </c>
-      <c r="D35" t="s">
-        <v>169</v>
-      </c>
       <c r="E35" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F35" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G35" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H35" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I35" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J35">
         <v>2</v>
@@ -2803,212 +2833,212 @@
         <v>22</v>
       </c>
       <c r="N35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B36" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="C36" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="D36" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E36" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F36" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="G36" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H36" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I36" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J36">
         <v>2</v>
       </c>
       <c r="K36" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="N36" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B37" t="s">
+        <v>184</v>
+      </c>
+      <c r="C37" t="s">
+        <v>185</v>
+      </c>
+      <c r="D37" t="s">
+        <v>186</v>
+      </c>
+      <c r="E37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F37" t="s">
+        <v>186</v>
+      </c>
+      <c r="G37" t="s">
+        <v>101</v>
+      </c>
+      <c r="H37" t="s">
+        <v>187</v>
+      </c>
+      <c r="I37" t="s">
+        <v>188</v>
+      </c>
+      <c r="J37">
+        <v>16</v>
+      </c>
+      <c r="K37" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37">
         <v>180</v>
-      </c>
-      <c r="C37" t="s">
-        <v>181</v>
-      </c>
-      <c r="D37" t="s">
-        <v>151</v>
-      </c>
-      <c r="E37" t="s">
-        <v>182</v>
-      </c>
-      <c r="F37" t="s">
-        <v>151</v>
-      </c>
-      <c r="G37" t="s">
-        <v>182</v>
-      </c>
-      <c r="H37" t="s">
-        <v>183</v>
-      </c>
-      <c r="I37" t="s">
-        <v>182</v>
-      </c>
-      <c r="J37">
-        <v>2</v>
-      </c>
-      <c r="K37" t="s">
-        <v>86</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
       </c>
       <c r="M37" t="s">
         <v>40</v>
       </c>
       <c r="N37" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B38" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C38" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D38" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E38" t="s">
-        <v>92</v>
+        <v>193</v>
       </c>
       <c r="F38" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="G38" t="s">
-        <v>92</v>
+        <v>193</v>
       </c>
       <c r="H38" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="I38" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="J38">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K38" t="s">
         <v>21</v>
       </c>
       <c r="L38">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M38" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="N38" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B39" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C39" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D39" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="E39" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="F39" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="G39" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="H39" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="I39" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K39" t="s">
         <v>21</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M39" t="s">
         <v>22</v>
       </c>
       <c r="N39" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B40" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C40" t="s">
+        <v>207</v>
+      </c>
+      <c r="D40" t="s">
         <v>200</v>
       </c>
-      <c r="D40" t="s">
-        <v>201</v>
-      </c>
       <c r="E40" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F40" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G40" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="H40" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="I40" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="J40">
         <v>3</v>
@@ -3023,80 +3053,80 @@
         <v>22</v>
       </c>
       <c r="N40" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B41" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C41" t="s">
-        <v>208</v>
+        <v>53</v>
       </c>
       <c r="D41" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="E41" t="s">
-        <v>209</v>
+        <v>55</v>
       </c>
       <c r="F41" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="G41" t="s">
-        <v>209</v>
+        <v>55</v>
       </c>
       <c r="H41" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I41" t="s">
-        <v>211</v>
+        <v>56</v>
       </c>
       <c r="J41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K41" t="s">
         <v>21</v>
       </c>
       <c r="L41">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M41" t="s">
         <v>22</v>
       </c>
       <c r="N41" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>215</v>
+      </c>
+      <c r="B42" t="s">
         <v>212</v>
-      </c>
-      <c r="B42" t="s">
-        <v>213</v>
       </c>
       <c r="C42" t="s">
         <v>53</v>
       </c>
       <c r="D42" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E42" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F42" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G42" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H42" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I42" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="J42">
         <v>2</v>
@@ -3111,7 +3141,7 @@
         <v>22</v>
       </c>
       <c r="N42" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -3119,28 +3149,28 @@
         <v>216</v>
       </c>
       <c r="B43" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C43" t="s">
         <v>53</v>
       </c>
       <c r="D43" t="s">
-        <v>214</v>
+        <v>66</v>
       </c>
       <c r="E43" t="s">
-        <v>63</v>
+        <v>217</v>
       </c>
       <c r="F43" t="s">
-        <v>214</v>
+        <v>66</v>
       </c>
       <c r="G43" t="s">
-        <v>63</v>
+        <v>217</v>
       </c>
       <c r="H43" t="s">
-        <v>214</v>
+        <v>68</v>
       </c>
       <c r="I43" t="s">
-        <v>64</v>
+        <v>217</v>
       </c>
       <c r="J43">
         <v>2</v>
@@ -3149,42 +3179,42 @@
         <v>21</v>
       </c>
       <c r="L43">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M43" t="s">
         <v>22</v>
       </c>
       <c r="N43" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B44" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C44" t="s">
-        <v>53</v>
+        <v>167</v>
       </c>
       <c r="D44" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="E44" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F44" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="G44" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H44" t="s">
-        <v>68</v>
+        <v>221</v>
       </c>
       <c r="I44" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J44">
         <v>2</v>
@@ -3193,42 +3223,42 @@
         <v>21</v>
       </c>
       <c r="L44">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M44" t="s">
         <v>22</v>
       </c>
       <c r="N44" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>223</v>
+      </c>
+      <c r="B45" t="s">
         <v>219</v>
       </c>
-      <c r="B45" t="s">
-        <v>220</v>
-      </c>
       <c r="C45" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D45" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E45" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F45" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G45" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H45" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="I45" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="J45">
         <v>2</v>
@@ -3237,42 +3267,42 @@
         <v>21</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M45" t="s">
         <v>22</v>
       </c>
       <c r="N45" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B46" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C46" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D46" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="E46" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F46" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="G46" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H46" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I46" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J46">
         <v>2</v>
@@ -3281,42 +3311,42 @@
         <v>21</v>
       </c>
       <c r="L46">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M46" t="s">
         <v>22</v>
       </c>
       <c r="N46" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B47" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C47" t="s">
-        <v>168</v>
+        <v>53</v>
       </c>
       <c r="D47" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E47" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F47" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="G47" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H47" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="I47" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J47">
         <v>2</v>
@@ -3325,42 +3355,42 @@
         <v>21</v>
       </c>
       <c r="L47">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M47" t="s">
         <v>22</v>
       </c>
       <c r="N47" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>234</v>
+      </c>
+      <c r="B48" t="s">
+        <v>235</v>
+      </c>
+      <c r="C48" t="s">
+        <v>167</v>
+      </c>
+      <c r="D48" t="s">
         <v>231</v>
       </c>
-      <c r="B48" t="s">
-        <v>213</v>
-      </c>
-      <c r="C48" t="s">
-        <v>53</v>
-      </c>
-      <c r="D48" t="s">
-        <v>232</v>
-      </c>
       <c r="E48" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F48" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G48" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="H48" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I48" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="J48">
         <v>2</v>
@@ -3369,42 +3399,42 @@
         <v>21</v>
       </c>
       <c r="L48">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M48" t="s">
         <v>22</v>
       </c>
       <c r="N48" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B49" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C49" t="s">
-        <v>168</v>
+        <v>53</v>
       </c>
       <c r="D49" t="s">
-        <v>232</v>
+        <v>132</v>
       </c>
       <c r="E49" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F49" t="s">
-        <v>232</v>
+        <v>132</v>
       </c>
       <c r="G49" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="H49" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="I49" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="J49">
         <v>2</v>
@@ -3413,42 +3443,42 @@
         <v>21</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M49" t="s">
         <v>22</v>
       </c>
       <c r="N49" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B50" t="s">
-        <v>241</v>
+        <v>212</v>
       </c>
       <c r="C50" t="s">
         <v>53</v>
       </c>
       <c r="D50" t="s">
-        <v>242</v>
+        <v>132</v>
       </c>
       <c r="E50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F50" t="s">
-        <v>242</v>
+        <v>132</v>
       </c>
       <c r="G50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J50">
         <v>2</v>
@@ -3457,42 +3487,42 @@
         <v>21</v>
       </c>
       <c r="L50">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M50" t="s">
         <v>22</v>
       </c>
       <c r="N50" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B51" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C51" t="s">
         <v>53</v>
       </c>
       <c r="D51" t="s">
-        <v>242</v>
+        <v>126</v>
       </c>
       <c r="E51" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F51" t="s">
-        <v>242</v>
+        <v>126</v>
       </c>
       <c r="G51" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H51" t="s">
+        <v>249</v>
+      </c>
+      <c r="I51" t="s">
         <v>248</v>
-      </c>
-      <c r="I51" t="s">
-        <v>247</v>
       </c>
       <c r="J51">
         <v>2</v>
@@ -3501,42 +3531,42 @@
         <v>21</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M51" t="s">
         <v>22</v>
       </c>
       <c r="N51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B52" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C52" t="s">
         <v>53</v>
       </c>
       <c r="D52" t="s">
-        <v>128</v>
+        <v>251</v>
       </c>
       <c r="E52" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F52" t="s">
-        <v>128</v>
+        <v>251</v>
       </c>
       <c r="G52" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H52" t="s">
         <v>251</v>
       </c>
       <c r="I52" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="J52">
         <v>2</v>
@@ -3545,39 +3575,39 @@
         <v>21</v>
       </c>
       <c r="L52">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M52" t="s">
         <v>22</v>
       </c>
       <c r="N52" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B53" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C53" t="s">
         <v>53</v>
       </c>
       <c r="D53" t="s">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="E53" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F53" t="s">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="G53" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H53" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I53" t="s">
         <v>255</v>
@@ -3589,42 +3619,42 @@
         <v>21</v>
       </c>
       <c r="L53">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M53" t="s">
         <v>22</v>
       </c>
       <c r="N53" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B54" t="s">
-        <v>213</v>
+        <v>258</v>
       </c>
       <c r="C54" t="s">
-        <v>53</v>
+        <v>259</v>
       </c>
       <c r="D54" t="s">
+        <v>260</v>
+      </c>
+      <c r="E54" t="s">
         <v>151</v>
       </c>
-      <c r="E54" t="s">
-        <v>257</v>
-      </c>
       <c r="F54" t="s">
+        <v>260</v>
+      </c>
+      <c r="G54" t="s">
         <v>151</v>
       </c>
-      <c r="G54" t="s">
-        <v>257</v>
-      </c>
       <c r="H54" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I54" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J54">
         <v>2</v>
@@ -3633,42 +3663,42 @@
         <v>21</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M54" t="s">
         <v>22</v>
       </c>
       <c r="N54" t="s">
-        <v>215</v>
+        <v>258</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>262</v>
+      </c>
+      <c r="B55" t="s">
+        <v>258</v>
+      </c>
+      <c r="C55" t="s">
         <v>259</v>
       </c>
-      <c r="B55" t="s">
-        <v>260</v>
-      </c>
-      <c r="C55" t="s">
-        <v>261</v>
-      </c>
       <c r="D55" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E55" t="s">
-        <v>152</v>
+        <v>264</v>
       </c>
       <c r="F55" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G55" t="s">
-        <v>152</v>
+        <v>264</v>
       </c>
       <c r="H55" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I55" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J55">
         <v>2</v>
@@ -3683,36 +3713,36 @@
         <v>22</v>
       </c>
       <c r="N55" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>266</v>
+      </c>
+      <c r="B56" t="s">
+        <v>258</v>
+      </c>
+      <c r="C56" t="s">
+        <v>259</v>
+      </c>
+      <c r="D56" t="s">
+        <v>106</v>
+      </c>
+      <c r="E56" t="s">
         <v>264</v>
       </c>
-      <c r="B56" t="s">
-        <v>260</v>
-      </c>
-      <c r="C56" t="s">
-        <v>261</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="F56" t="s">
+        <v>106</v>
+      </c>
+      <c r="G56" t="s">
+        <v>264</v>
+      </c>
+      <c r="H56" t="s">
+        <v>106</v>
+      </c>
+      <c r="I56" t="s">
         <v>265</v>
-      </c>
-      <c r="E56" t="s">
-        <v>266</v>
-      </c>
-      <c r="F56" t="s">
-        <v>265</v>
-      </c>
-      <c r="G56" t="s">
-        <v>266</v>
-      </c>
-      <c r="H56" t="s">
-        <v>265</v>
-      </c>
-      <c r="I56" t="s">
-        <v>267</v>
       </c>
       <c r="J56">
         <v>2</v>
@@ -3727,36 +3757,36 @@
         <v>22</v>
       </c>
       <c r="N56" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>267</v>
+      </c>
+      <c r="B57" t="s">
         <v>268</v>
       </c>
-      <c r="B57" t="s">
-        <v>260</v>
-      </c>
       <c r="C57" t="s">
-        <v>261</v>
+        <v>167</v>
       </c>
       <c r="D57" t="s">
-        <v>108</v>
+        <v>233</v>
       </c>
       <c r="E57" t="s">
-        <v>266</v>
+        <v>39</v>
       </c>
       <c r="F57" t="s">
-        <v>108</v>
+        <v>233</v>
       </c>
       <c r="G57" t="s">
-        <v>266</v>
+        <v>39</v>
       </c>
       <c r="H57" t="s">
-        <v>108</v>
+        <v>233</v>
       </c>
       <c r="I57" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J57">
         <v>2</v>
@@ -3771,36 +3801,36 @@
         <v>22</v>
       </c>
       <c r="N57" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B58" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C58" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D58" t="s">
-        <v>234</v>
+        <v>76</v>
       </c>
       <c r="E58" t="s">
-        <v>39</v>
+        <v>272</v>
       </c>
       <c r="F58" t="s">
-        <v>234</v>
+        <v>76</v>
       </c>
       <c r="G58" t="s">
-        <v>39</v>
+        <v>272</v>
       </c>
       <c r="H58" t="s">
-        <v>234</v>
+        <v>273</v>
       </c>
       <c r="I58" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J58">
         <v>2</v>
@@ -3809,42 +3839,42 @@
         <v>21</v>
       </c>
       <c r="L58">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M58" t="s">
         <v>22</v>
       </c>
       <c r="N58" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B59" t="s">
-        <v>270</v>
+        <v>75</v>
       </c>
       <c r="C59" t="s">
-        <v>168</v>
+        <v>53</v>
       </c>
       <c r="D59" t="s">
-        <v>76</v>
+        <v>275</v>
       </c>
       <c r="E59" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F59" t="s">
-        <v>76</v>
+        <v>275</v>
       </c>
       <c r="G59" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H59" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I59" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J59">
         <v>2</v>
@@ -3853,42 +3883,42 @@
         <v>21</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M59" t="s">
         <v>22</v>
       </c>
       <c r="N59" t="s">
-        <v>272</v>
+        <v>79</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B60" t="s">
-        <v>75</v>
+        <v>279</v>
       </c>
       <c r="C60" t="s">
         <v>53</v>
       </c>
       <c r="D60" t="s">
-        <v>277</v>
+        <v>76</v>
       </c>
       <c r="E60" t="s">
-        <v>278</v>
+        <v>127</v>
       </c>
       <c r="F60" t="s">
-        <v>277</v>
+        <v>76</v>
       </c>
       <c r="G60" t="s">
-        <v>278</v>
+        <v>127</v>
       </c>
       <c r="H60" t="s">
-        <v>279</v>
+        <v>78</v>
       </c>
       <c r="I60" t="s">
-        <v>278</v>
+        <v>127</v>
       </c>
       <c r="J60">
         <v>2</v>
@@ -3897,42 +3927,42 @@
         <v>21</v>
       </c>
       <c r="L60">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M60" t="s">
         <v>22</v>
       </c>
       <c r="N60" t="s">
-        <v>79</v>
+        <v>280</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B61" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C61" t="s">
-        <v>53</v>
+        <v>167</v>
       </c>
       <c r="D61" t="s">
         <v>76</v>
       </c>
       <c r="E61" t="s">
-        <v>129</v>
+        <v>283</v>
       </c>
       <c r="F61" t="s">
         <v>76</v>
       </c>
       <c r="G61" t="s">
-        <v>129</v>
+        <v>283</v>
       </c>
       <c r="H61" t="s">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="I61" t="s">
-        <v>129</v>
+        <v>283</v>
       </c>
       <c r="J61">
         <v>2</v>
@@ -3947,36 +3977,36 @@
         <v>22</v>
       </c>
       <c r="N61" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B62" t="s">
-        <v>284</v>
+        <v>118</v>
       </c>
       <c r="C62" t="s">
-        <v>168</v>
+        <v>53</v>
       </c>
       <c r="D62" t="s">
-        <v>76</v>
+        <v>286</v>
       </c>
       <c r="E62" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F62" t="s">
-        <v>76</v>
+        <v>286</v>
       </c>
       <c r="G62" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H62" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="I62" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J62">
         <v>2</v>
@@ -3985,42 +4015,42 @@
         <v>21</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M62" t="s">
         <v>22</v>
       </c>
       <c r="N62" t="s">
-        <v>286</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B63" t="s">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="C63" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="D63" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E63" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F63" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G63" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H63" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I63" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="J63">
         <v>2</v>
@@ -4029,13 +4059,57 @@
         <v>21</v>
       </c>
       <c r="L63">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M63" t="s">
         <v>22</v>
       </c>
       <c r="N63" t="s">
-        <v>124</v>
+        <v>294</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>295</v>
+      </c>
+      <c r="B64" t="s">
+        <v>296</v>
+      </c>
+      <c r="C64" t="s">
+        <v>297</v>
+      </c>
+      <c r="D64" t="s">
+        <v>298</v>
+      </c>
+      <c r="E64" t="s">
+        <v>292</v>
+      </c>
+      <c r="F64" t="s">
+        <v>298</v>
+      </c>
+      <c r="G64" t="s">
+        <v>292</v>
+      </c>
+      <c r="H64" t="s">
+        <v>298</v>
+      </c>
+      <c r="I64" t="s">
+        <v>299</v>
+      </c>
+      <c r="J64">
+        <v>2</v>
+      </c>
+      <c r="K64" t="s">
+        <v>21</v>
+      </c>
+      <c r="L64">
+        <v>270</v>
+      </c>
+      <c r="M64" t="s">
+        <v>22</v>
+      </c>
+      <c r="N64" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
